--- a/data/gravel/State Carbon All-Road 2025.xlsx
+++ b/data/gravel/State Carbon All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E6D9DA-89AB-844F-82E1-D31C6D8F01F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4C3B2E-445A-D94C-8982-470E0F32FB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="500" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,9 +269,6 @@
     <t>Stack</t>
   </si>
   <si>
-    <t>both</t>
-  </si>
-  <si>
     <t>Measurement</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>drop bar</t>
   </si>
 </sst>
 </file>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -759,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -802,7 +802,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -819,22 +819,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="7">
         <v>78</v>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="7">
         <v>435</v>
@@ -888,7 +888,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="7">
         <v>165</v>
@@ -911,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="7">
         <v>541</v>
@@ -934,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="7">
         <v>50</v>
@@ -957,7 +957,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="7">
         <v>90</v>
@@ -980,7 +980,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="7">
         <v>71.2</v>
@@ -1026,7 +1026,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="7">
         <v>490</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="7">
         <v>74.099999999999994</v>
@@ -1095,7 +1095,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" s="1">
         <f>VALUE(LEFT(H20,5)) * 25.4</f>
@@ -1118,19 +1118,19 @@
         <v>843.02599999999984</v>
       </c>
       <c r="H20" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="K20" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1138,7 +1138,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="7">
         <v>1025</v>
@@ -1398,19 +1398,19 @@
         <v>67</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="G36" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -1418,7 +1418,7 @@
         <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1434,7 +1434,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1507,7 +1507,7 @@
         <v>42</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1561,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
